--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>283.17</v>
+        <v>160.06</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>45.18</v>
+        <v>51.7</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>147.28</v>
+        <v>60.37</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.23 ± 0.09</t>
+          <t>4.65 ± 0.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.28 ± 0.11</t>
+          <t>0.32 ± 0.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.46 ± 0.64</t>
+          <t>0.86 ± 0.27</t>
         </is>
       </c>
     </row>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109.03</v>
+        <v>111.63</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>106.57</v>
+        <v>40.78</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>24.04</v>
+        <v>53.38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.02 ± 0.28</t>
+          <t>0.66 ± 0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.07 ± 0.39</t>
+          <t>5.83 ± 0.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.10 ± 0.50</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71.43000000000001</v>
+        <v>35.59</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>91.56</v>
+        <v>54.71</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>18.34</v>
+        <v>12.69</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.80 ± 0.27</t>
+          <t>5.11 ± 0.30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.65 ± 0.55</t>
+          <t>3.38 ± 1.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.62 ± 0.17</t>
+          <t>6.45 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.89</v>
+        <v>5.73</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>82.11</v>
+        <v>15.92</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>16.28</v>
+        <v>7.02</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0025**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.31 ± 0.12</t>
+          <t>0.82 ± 0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.84 ± 0.67</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.13 ± 0.64</t>
+          <t>0.10 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43.58</v>
+        <v>18.25</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>113.3</v>
+        <v>66.38</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>9.039999999999999</v>
+        <v>5.36</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0005***</t>
+          <t>0.0088**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.04 ± 0.33</t>
+          <t>1.01 ± 0.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.39 ± 0.20</t>
+          <t>2.48 ± 1.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.42 ± 0.30</t>
+          <t>0.19 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.48</v>
+        <v>19.5</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>40.22</v>
+        <v>128.2</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>6.71</v>
+        <v>2.97</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0027**</t>
+          <t>0.0632.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.27 ± 0.13</t>
+          <t>2.59 ± 0.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.21 ± 0.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.38 ± 0.51</t>
+          <t>2.44 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.08</v>
+        <v>2.93</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>18.44</v>
+        <v>26.83</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>2.13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0091**</t>
+          <t>0.1324</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.11 ± 0.06</t>
+          <t>0.55 ± 0.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.30 ± 0.30</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.85 ± 0.32</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
     </row>
@@ -805,28 +805,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>4.62</v>
+        <v>1.27</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1020</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.05 ± 0.03</t>
+          <t>0.11 ± 0.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.28 ± 0.20</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.77</v>
+        <v>0.3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>30.13</v>
+        <v>3.96</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>1.49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1269</t>
+          <t>0.2378</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.57 ± 0.16</t>
+          <t>0.17 ± 0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.06 ± 0.06</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.80 ± 0.28</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>8.52</v>
+        <v>13.66</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1556</t>
+          <t>0.2947</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.12 ± 0.06</t>
+          <t>0.29 ± 0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.32 ± 0.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.37 ± 0.25</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -936,32 +936,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.87</v>
+        <v>1.12</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>48.38</v>
+        <v>17.8</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>1.88</v>
+        <v>1.23</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.1640</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.61 ± 0.21</t>
+          <t>0.37 ± 0.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.87 ± 0.32</t>
+          <t>0.06 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.45</v>
+        <v>0.74</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>62.3</v>
+        <v>12.17</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.3175</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.57 ± 0.23</t>
+          <t>0.29 ± 0.16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.96 ± 0.39</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>12.48</v>
+        <v>7.62</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.2651</t>
+          <t>0.3701</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.19 ± 0.09</t>
+          <t>0.25 ± 0.12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.47 ± 0.23</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.10 ± 0.10</t>
+          <t>0.08 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.79</v>
+        <v>0.74</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>56.01</v>
+        <v>16.38</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>1.17</v>
+        <v>0.88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.62 ± 0.24</t>
+          <t>0.40 ± 0.15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.42 ± 0.42</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.35 ± 0.21</t>
+          <t>0.13 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -1116,32 +1116,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>7.38</v>
+        <v>7.32</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>0.86</v>
+        <v>0.44</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.6458</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.08 ± 0.07</t>
+          <t>0.13 ± 0.13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.23 ± 0.19</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>16.24</v>
+        <v>0.47</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
         <v>0.44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.6464</t>
+          <t>0.6458</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.24 ± 0.08</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.40 ± 0.33</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.14 ± 0.14</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160.06</v>
+        <v>157.98</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>51.7</v>
+        <v>69.52</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>60.37</v>
+        <v>63.63</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.65 ± 0.27</t>
+          <t>0.54 ± 0.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.32 ± 0.32</t>
+          <t>4.24 ± 0.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.86 ± 0.27</t>
+          <t>4.58 ± 0.35</t>
         </is>
       </c>
     </row>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>111.63</v>
+        <v>37.42</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>40.78</v>
+        <v>44.58</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>53.38</v>
+        <v>23.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.66 ± 0.29</t>
+          <t>0.26 ± 0.10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.83 ± 0.30</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>2.84 ± 0.87</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.59</v>
+        <v>37.74</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>54.71</v>
+        <v>53.85</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>12.69</v>
+        <v>19.62</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0001***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.11 ± 0.30</t>
+          <t>5.34 ± 0.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.38 ± 1.03</t>
+          <t>4.34 ± 0.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6.45 ± 0.07</t>
+          <t>2.79 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.73</v>
+        <v>47.35</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>15.92</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>7.02</v>
+        <v>14.13</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0025**</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.82 ± 0.18</t>
+          <t>4.86 ± 0.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>2.82 ± 0.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.10 ± 0.07</t>
+          <t>2.66 ± 0.52</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.25</v>
+        <v>29.5</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>66.38</v>
+        <v>65.73</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>5.36</v>
+        <v>12.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0088**</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.01 ± 0.28</t>
+          <t>0.21 ± 0.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.48 ± 1.48</t>
+          <t>1.13 ± 0.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.19 ± 0.13</t>
+          <t>2.45 ± 1.05</t>
         </is>
       </c>
     </row>
@@ -715,38 +715,38 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.5</v>
+        <v>43.34</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>128.2</v>
+        <v>96.95</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.97</v>
+        <v>12.52</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0632.</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.59 ± 0.41</t>
+          <t>2.10 ± 0.20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.21 ± 0.21</t>
+          <t>4.12 ± 0.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.44 ± 0.46</t>
+          <t>0.70 ± 0.47</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.93</v>
+        <v>25.5</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>26.83</v>
+        <v>76.81</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.1324</t>
+          <t>0.0003***</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.55 ± 0.24</t>
+          <t>0.67 ± 0.17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.31 ± 0.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>2.75 ± 0.69</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.12</v>
+        <v>7.38</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1.27</v>
+        <v>61.83</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>3.34</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.0426*</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.11 ± 0.05</t>
+          <t>0.46 ± 0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.13 ± 0.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.52 ± 0.84</t>
         </is>
       </c>
     </row>
@@ -850,38 +850,38 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3</v>
+        <v>3.53</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3.96</v>
+        <v>34.91</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.49</v>
+        <v>2.83</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.2378</t>
+          <t>0.0673.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.17 ± 0.09</t>
+          <t>0.32 ± 0.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.86 ± 0.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.94 ± 0.63</t>
         </is>
       </c>
     </row>
@@ -891,37 +891,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.88</v>
+        <v>1.59</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>13.66</v>
+        <v>18.97</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2947</t>
+          <t>0.1049</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.29 ± 0.16</t>
+          <t>0.16 ± 0.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.32 ± 0.32</t>
+          <t>0.60 ± 0.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.12</v>
+        <v>2.45</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>17.8</v>
+        <v>68.83</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.3749</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.37 ± 0.19</t>
+          <t>0.85 ± 0.17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.10 ± 0.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.06 ± 0.05</t>
+          <t>0.28 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>12.17</v>
+        <v>34.78</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>0.91</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.3175</t>
+          <t>0.4066</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.29 ± 0.16</t>
+          <t>0.61 ± 0.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.21 ± 0.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>0.49 ± 0.33</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4</v>
+        <v>1.32</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>7.62</v>
+        <v>43.6</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.4348</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.25 ± 0.12</t>
+          <t>0.41 ± 0.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>0.61 ± 0.34</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.08 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.74</v>
+        <v>0.21</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>16.38</v>
+        <v>10.93</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.5908</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.40 ± 0.15</t>
+          <t>0.10 ± 0.06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.42 ± 0.42</t>
+          <t>0.24 ± 0.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.13 ± 0.12</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.17</v>
+        <v>0.88</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>7.32</v>
+        <v>50.38</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.6458</t>
+          <t>0.6151</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.13 ± 0.13</t>
+          <t>0.52 ± 0.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.16 ± 0.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.41 ± 0.39</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01</v>
+        <v>1.62</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.47</v>
+        <v>103.77</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
         <v>0.44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.6458</t>
+          <t>0.6485</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>0.83 ± 0.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.82 ± 0.36</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.38 ± 0.54</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157.98</v>
+        <v>116.84</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>69.52</v>
+        <v>65.87</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>63.63</v>
+        <v>43.46</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.15</t>
+          <t>0.33 ± 0.10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.24 ± 0.65</t>
+          <t>3.42 ± 0.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.58 ± 0.35</t>
+          <t>3.77 ± 0.51</t>
         </is>
       </c>
     </row>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37.42</v>
+        <v>35.2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>44.58</v>
+        <v>43.04</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>23.5</v>
+        <v>20.04</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.26 ± 0.10</t>
+          <t>0.33 ± 0.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.84 ± 0.87</t>
+          <t>3.00 ± 1.05</t>
         </is>
       </c>
     </row>
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.74</v>
+        <v>32.31</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>53.85</v>
+        <v>47.72</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>19.62</v>
+        <v>16.59</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -601,17 +601,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.34 ± 0.12</t>
+          <t>5.46 ± 0.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.34 ± 0.64</t>
+          <t>4.07 ± 0.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.79 ± 0.32</t>
+          <t>3.27 ± 0.54</t>
         </is>
       </c>
     </row>
@@ -621,23 +621,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.35</v>
+        <v>35.68</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>93.84999999999999</v>
+        <v>57.01</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>14.13</v>
+        <v>15.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,17 +646,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.86 ± 0.19</t>
+          <t>0.22 ± 0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.82 ± 0.54</t>
+          <t>0.76 ± 0.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.66 ± 0.52</t>
+          <t>3.06 ± 1.09</t>
         </is>
       </c>
     </row>
@@ -666,23 +666,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.5</v>
+        <v>42.56</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>65.73</v>
+        <v>73.78</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>12.57</v>
+        <v>14.13</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.21 ± 0.08</t>
+          <t>1.90 ± 0.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.13 ± 0.61</t>
+          <t>3.55 ± 0.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.45 ± 1.05</t>
+          <t>0.30 ± 0.30</t>
         </is>
       </c>
     </row>
@@ -711,23 +711,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43.34</v>
+        <v>23.65</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>96.95</v>
+        <v>43.54</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>12.52</v>
+        <v>13.31</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -736,17 +736,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.10 ± 0.20</t>
+          <t>0.35 ± 0.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.12 ± 0.47</t>
+          <t>0.35 ± 0.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.70 ± 0.47</t>
+          <t>2.64 ± 0.93</t>
         </is>
       </c>
     </row>
@@ -760,38 +760,38 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25.5</v>
+        <v>28.28</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>76.81</v>
+        <v>62.97</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>9.300000000000001</v>
+        <v>11.01</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0003***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.67 ± 0.17</t>
+          <t>0.29 ± 0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.31 ± 0.22</t>
+          <t>1.84 ± 0.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.75 ± 0.69</t>
+          <t>1.92 ± 0.34</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.38</v>
+        <v>7.02</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>61.83</v>
+        <v>26.61</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>3.34</v>
+        <v>6.46</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0426*</t>
+          <t>0.0032**</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.46 ± 0.14</t>
+          <t>0.24 ± 0.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.13 ± 0.13</t>
+          <t>1.09 ± 0.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.52 ± 0.84</t>
+          <t>0.07 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.53</v>
+        <v>8.92</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>34.91</v>
+        <v>35.08</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83</v>
+        <v>6.23</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0673.</t>
+          <t>0.0039**</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.32 ± 0.08</t>
+          <t>0.23 ± 0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.86 ± 0.40</t>
+          <t>1.17 ± 0.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.94 ± 0.63</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.59</v>
+        <v>14.8</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>18.97</v>
+        <v>109.05</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>2.35</v>
+        <v>3.33</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1049</t>
+          <t>0.0442*</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.16 ± 0.08</t>
+          <t>4.79 ± 0.23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.60 ± 0.36</t>
+          <t>3.84 ± 0.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>3.33 ± 0.78</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.45</v>
+        <v>1.19</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>68.83</v>
+        <v>17.56</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3749</t>
+          <t>0.2010</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.85 ± 0.17</t>
+          <t>0.13 ± 0.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.10 ± 0.44</t>
+          <t>0.46 ± 0.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.28 ± 0.25</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -985,38 +985,38 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>34.78</v>
+        <v>32.14</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.4066</t>
+          <t>0.3877</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.61 ± 0.12</t>
+          <t>0.52 ± 0.13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.21 ± 0.12</t>
+          <t>0.52 ± 0.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.49 ± 0.33</t>
+          <t>1.05 ± 0.48</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.32</v>
+        <v>0.87</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>43.6</v>
+        <v>45.33</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>0.85</v>
+        <v>0.47</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.4348</t>
+          <t>0.6266</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.41 ± 0.14</t>
+          <t>0.55 ± 0.18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.61 ± 0.34</t>
+          <t>0.28 ± 0.18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.26 ± 0.24</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.21</v>
+        <v>0.87</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>10.93</v>
+        <v>58.26</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.5908</t>
+          <t>0.6955</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.10 ± 0.06</t>
+          <t>0.79 ± 0.19</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.24 ± 0.24</t>
+          <t>1.03 ± 0.31</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.58 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>50.38</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.6151</t>
+          <t>0.7733</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.52 ± 0.15</t>
+          <t>0.88 ± 0.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.16 ± 0.13</t>
+          <t>1.12 ± 0.32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.41 ± 0.39</t>
+          <t>1.29 ± 0.65</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.62</v>
+        <v>0.09</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>103.77</v>
+        <v>10.95</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.6485</t>
+          <t>0.8144</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.83 ± 0.21</t>
+          <t>0.13 ± 0.08</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.82 ± 0.36</t>
+          <t>0.16 ± 0.16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.38 ± 0.54</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.84</v>
+        <v>157.98</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>65.87</v>
+        <v>69.52</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>43.46</v>
+        <v>63.63</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.33 ± 0.10</t>
+          <t>0.54 ± 0.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.42 ± 0.61</t>
+          <t>4.24 ± 0.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.77 ± 0.51</t>
+          <t>4.58 ± 0.35</t>
         </is>
       </c>
     </row>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35.2</v>
+        <v>37.42</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>43.04</v>
+        <v>44.58</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>20.04</v>
+        <v>23.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.33 ± 0.13</t>
+          <t>0.26 ± 0.10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.00 ± 1.05</t>
+          <t>2.84 ± 0.87</t>
         </is>
       </c>
     </row>
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.31</v>
+        <v>37.74</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>47.72</v>
+        <v>53.85</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>16.59</v>
+        <v>19.62</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -601,17 +601,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.46 ± 0.13</t>
+          <t>5.34 ± 0.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.07 ± 0.42</t>
+          <t>4.34 ± 0.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.27 ± 0.54</t>
+          <t>2.79 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -621,23 +621,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.68</v>
+        <v>47.35</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>57.01</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>15.33</v>
+        <v>14.13</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,17 +646,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.22 ± 0.09</t>
+          <t>4.86 ± 0.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.76 ± 0.43</t>
+          <t>2.82 ± 0.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.06 ± 1.09</t>
+          <t>2.66 ± 0.52</t>
         </is>
       </c>
     </row>
@@ -666,23 +666,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>42.56</v>
+        <v>29.5</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>73.78</v>
+        <v>65.73</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>14.13</v>
+        <v>12.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.90 ± 0.22</t>
+          <t>0.21 ± 0.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.55 ± 0.33</t>
+          <t>1.13 ± 0.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.30 ± 0.30</t>
+          <t>2.45 ± 1.05</t>
         </is>
       </c>
     </row>
@@ -711,23 +711,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.65</v>
+        <v>43.34</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>43.54</v>
+        <v>96.95</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>13.31</v>
+        <v>12.52</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -736,17 +736,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.35 ± 0.13</t>
+          <t>2.10 ± 0.20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.35 ± 0.21</t>
+          <t>4.12 ± 0.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.64 ± 0.93</t>
+          <t>0.70 ± 0.47</t>
         </is>
       </c>
     </row>
@@ -760,38 +760,38 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.28</v>
+        <v>25.5</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>62.97</v>
+        <v>76.81</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>11.01</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0001***</t>
+          <t>0.0003***</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.29 ± 0.14</t>
+          <t>0.67 ± 0.17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.84 ± 0.53</t>
+          <t>0.31 ± 0.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.92 ± 0.34</t>
+          <t>2.75 ± 0.69</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.02</v>
+        <v>7.38</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>26.61</v>
+        <v>61.83</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>6.46</v>
+        <v>3.34</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0032**</t>
+          <t>0.0426*</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.24 ± 0.08</t>
+          <t>0.46 ± 0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.09 ± 0.37</t>
+          <t>0.13 ± 0.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.07 ± 0.07</t>
+          <t>1.52 ± 0.84</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.92</v>
+        <v>3.53</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>35.08</v>
+        <v>34.91</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>6.23</v>
+        <v>2.83</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0039**</t>
+          <t>0.0673.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.23 ± 0.09</t>
+          <t>0.32 ± 0.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.17 ± 0.45</t>
+          <t>0.86 ± 0.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.94 ± 0.63</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.8</v>
+        <v>1.59</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>109.05</v>
+        <v>18.97</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0442*</t>
+          <t>0.1049</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.79 ± 0.23</t>
+          <t>0.16 ± 0.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.84 ± 0.51</t>
+          <t>0.60 ± 0.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.33 ± 0.78</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.19</v>
+        <v>2.45</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>17.56</v>
+        <v>68.83</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.66</v>
+        <v>1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.2010</t>
+          <t>0.3749</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.13 ± 0.08</t>
+          <t>0.85 ± 0.17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.46 ± 0.27</t>
+          <t>1.10 ± 0.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.28 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -985,38 +985,38 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>32.14</v>
+        <v>34.78</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.3877</t>
+          <t>0.4066</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.52 ± 0.13</t>
+          <t>0.61 ± 0.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.52 ± 0.24</t>
+          <t>0.21 ± 0.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.05 ± 0.48</t>
+          <t>0.49 ± 0.33</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.87</v>
+        <v>1.32</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>45.33</v>
+        <v>43.6</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>0.47</v>
+        <v>0.85</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.6266</t>
+          <t>0.4348</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.55 ± 0.18</t>
+          <t>0.41 ± 0.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.28 ± 0.18</t>
+          <t>0.61 ± 0.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.26 ± 0.24</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.87</v>
+        <v>0.21</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>58.26</v>
+        <v>10.93</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.37</v>
+        <v>0.53</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6955</t>
+          <t>0.5908</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.79 ± 0.19</t>
+          <t>0.10 ± 0.06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.03 ± 0.31</t>
+          <t>0.24 ± 0.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.58 ± 0.32</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>99.45999999999999</v>
+        <v>50.38</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.7733</t>
+          <t>0.6151</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.88 ± 0.26</t>
+          <t>0.52 ± 0.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.12 ± 0.32</t>
+          <t>0.16 ± 0.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.29 ± 0.65</t>
+          <t>0.41 ± 0.39</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.09</v>
+        <v>1.62</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>10.95</v>
+        <v>103.77</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.8144</t>
+          <t>0.6485</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.13 ± 0.08</t>
+          <t>0.83 ± 0.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.16 ± 0.16</t>
+          <t>0.82 ± 0.36</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.38 ± 0.54</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
